--- a/testData/FindOrderById.xlsx
+++ b/testData/FindOrderById.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14280" windowHeight="4788"/>
   </bookViews>
   <sheets>
     <sheet name="FindOrderById" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>orderId</t>
   </si>
@@ -49,31 +49,7 @@
     <t>TC_05</t>
   </si>
   <si>
-    <t>TC_06</t>
-  </si>
-  <si>
     <t>out_of_range</t>
-  </si>
-  <si>
-    <t>TC_07</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>bad_request</t>
-  </si>
-  <si>
-    <t>TC_08</t>
-  </si>
-  <si>
-    <t>TC_09</t>
-  </si>
-  <si>
-    <t>TC_10</t>
-  </si>
-  <si>
-    <t>TC_11</t>
   </si>
 </sst>
 </file>
@@ -117,16 +93,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.5546875" customWidth="1"/>
@@ -486,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -500,7 +473,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C5" s="2">
         <v>404</v>
@@ -514,97 +487,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>-1</v>
+        <v>25500</v>
       </c>
       <c r="C6" s="2">
         <v>404</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" s="2">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>404</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2">
-        <v>400</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2">
-        <v>25500</v>
-      </c>
-      <c r="C9" s="2">
-        <v>404</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>200</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2">
-        <v>3</v>
-      </c>
-      <c r="C11" s="2">
-        <v>200</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2">
-        <v>4</v>
-      </c>
-      <c r="C12" s="2">
-        <v>200</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
